--- a/db/A7XLK-4101-EpidemicShopping.xlsx
+++ b/db/A7XLK-4101-EpidemicShopping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4825140A-E39C-CC4F-B6E5-618EF82BFDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54008D0-C342-0347-8A0A-9517C8A40A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3960" windowWidth="39960" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="129">
   <si>
     <t>title</t>
   </si>
@@ -420,6 +420,112 @@
   </si>
   <si>
     <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-04.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>219</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-19.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.superbuy.com.tw/collection_fast.php?main_cate=608</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperBuy 市集</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2706-9229</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週一到週五 09:30-18:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北市敦化南路二段46號4F-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>220</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>悠活農村</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.yooho.com.tw/category.php?id=31</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北市松山區南京東路五段202號14樓之4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2748-0366</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週一至週五 09:00-18:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-20.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.healthyfood.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>221</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>棉花田 購物網</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-21.jpeg</t>
+  </si>
+  <si>
+    <t>0800-238-888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8:30-12:00；13:00-17:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北市大安區信義路四段236號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>222</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鮮拾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.pickup.com.tw/categories/vegetable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-22.jpeg</t>
+  </si>
+  <si>
+    <t>02-7737-1995</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週一至週五，9:30-12:00 13:00-18:30</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -786,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="2"/>
@@ -828,25 +934,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>8</v>
@@ -854,16 +960,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>110</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>8</v>
@@ -871,25 +986,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>118</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>8</v>
@@ -897,25 +1012,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>8</v>
@@ -923,25 +1035,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>8</v>
@@ -949,25 +1061,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>8</v>
@@ -975,25 +1078,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>8</v>
@@ -1001,16 +1104,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -1018,19 +1130,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>8</v>
@@ -1038,77 +1156,68 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>78</v>
+        <v>39</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>8</v>
@@ -1116,25 +1225,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>8</v>
@@ -1142,75 +1245,183 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="H19" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{FF014F7F-4D9F-954D-9D3B-692B924BD113}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{FA93F27D-9757-8B48-A778-815D241A5139}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{E5A6B5C2-735A-0B4F-8E2D-3A183FD797D7}"/>
-    <hyperlink ref="C4" r:id="rId4" xr:uid="{F329031C-14C4-CB42-BEF0-AA0A57289E77}"/>
-    <hyperlink ref="G8" r:id="rId5" xr:uid="{67A0EF08-2078-984E-9FA0-E0CA59DF625F}"/>
-    <hyperlink ref="G5" r:id="rId6" xr:uid="{1341D86C-65B0-FF4B-B0D2-A92F32A5ED23}"/>
-    <hyperlink ref="C5" r:id="rId7" xr:uid="{7495231B-1672-C146-B7FC-631236A6F827}"/>
-    <hyperlink ref="G6" r:id="rId8" xr:uid="{B845A19E-0F6D-414D-9702-DFA096F8CD2E}"/>
-    <hyperlink ref="C6" r:id="rId9" xr:uid="{BC42372E-EE9F-374C-BD27-6002B1396817}"/>
-    <hyperlink ref="G7" r:id="rId10" xr:uid="{27DD88BF-3CFD-6545-9FCB-C606BC361F1E}"/>
-    <hyperlink ref="G9" r:id="rId11" xr:uid="{ADB8327B-35FB-4A41-9EC0-A48CAD848492}"/>
-    <hyperlink ref="G10" r:id="rId12" xr:uid="{DC2FEEFD-4193-2444-9818-94C37DD84A42}"/>
-    <hyperlink ref="G11" r:id="rId13" xr:uid="{B54C8678-C102-5649-9328-2B56836CE8BD}"/>
-    <hyperlink ref="G12" r:id="rId14" xr:uid="{21B0F2B4-E3BB-334F-BDC3-F0365392ACA3}"/>
-    <hyperlink ref="G13" r:id="rId15" xr:uid="{D8D90138-54F9-5840-BE5B-D0EEEA00B9F3}"/>
-    <hyperlink ref="G14" r:id="rId16" xr:uid="{AC54B36E-7845-EE4B-8751-6B9EE967A5BA}"/>
-    <hyperlink ref="C14" r:id="rId17" xr:uid="{F67959B0-DCCF-4E42-9B06-36BA7ED31ADB}"/>
-    <hyperlink ref="G15" r:id="rId18" xr:uid="{0787AF62-22FC-DC46-BE6E-5068C08E2470}"/>
-    <hyperlink ref="G16" r:id="rId19" xr:uid="{FCCCB34D-6605-C34C-BA29-BEFD401ED8C3}"/>
+    <hyperlink ref="G6" r:id="rId1" xr:uid="{FF014F7F-4D9F-954D-9D3B-692B924BD113}"/>
+    <hyperlink ref="G7" r:id="rId2" xr:uid="{FA93F27D-9757-8B48-A778-815D241A5139}"/>
+    <hyperlink ref="G8" r:id="rId3" xr:uid="{E5A6B5C2-735A-0B4F-8E2D-3A183FD797D7}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{F329031C-14C4-CB42-BEF0-AA0A57289E77}"/>
+    <hyperlink ref="G12" r:id="rId5" xr:uid="{67A0EF08-2078-984E-9FA0-E0CA59DF625F}"/>
+    <hyperlink ref="G9" r:id="rId6" xr:uid="{1341D86C-65B0-FF4B-B0D2-A92F32A5ED23}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{7495231B-1672-C146-B7FC-631236A6F827}"/>
+    <hyperlink ref="G10" r:id="rId8" xr:uid="{B845A19E-0F6D-414D-9702-DFA096F8CD2E}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{BC42372E-EE9F-374C-BD27-6002B1396817}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{27DD88BF-3CFD-6545-9FCB-C606BC361F1E}"/>
+    <hyperlink ref="G13" r:id="rId11" xr:uid="{ADB8327B-35FB-4A41-9EC0-A48CAD848492}"/>
+    <hyperlink ref="G14" r:id="rId12" xr:uid="{DC2FEEFD-4193-2444-9818-94C37DD84A42}"/>
+    <hyperlink ref="G15" r:id="rId13" xr:uid="{B54C8678-C102-5649-9328-2B56836CE8BD}"/>
+    <hyperlink ref="G16" r:id="rId14" xr:uid="{21B0F2B4-E3BB-334F-BDC3-F0365392ACA3}"/>
+    <hyperlink ref="G17" r:id="rId15" xr:uid="{D8D90138-54F9-5840-BE5B-D0EEEA00B9F3}"/>
+    <hyperlink ref="G18" r:id="rId16" xr:uid="{AC54B36E-7845-EE4B-8751-6B9EE967A5BA}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{F67959B0-DCCF-4E42-9B06-36BA7ED31ADB}"/>
+    <hyperlink ref="G19" r:id="rId18" xr:uid="{0787AF62-22FC-DC46-BE6E-5068C08E2470}"/>
+    <hyperlink ref="G20" r:id="rId19" xr:uid="{FCCCB34D-6605-C34C-BA29-BEFD401ED8C3}"/>
+    <hyperlink ref="G2" r:id="rId20" xr:uid="{42B6BF2C-BE71-5A4E-8D4F-AB763946CE5E}"/>
+    <hyperlink ref="G3" r:id="rId21" xr:uid="{728DE385-385F-C740-B97D-C79D7F4A48C4}"/>
+    <hyperlink ref="G4" r:id="rId22" xr:uid="{AE5B6A88-CA07-AE49-83FB-A1B634F4900A}"/>
+    <hyperlink ref="G5" r:id="rId23" xr:uid="{ABE94E79-889E-0241-85F9-F200D3405B95}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>
